--- a/合联发票模板.xlsx
+++ b/合联发票模板.xlsx
@@ -24,98 +24,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="ID_4044FAE9DFDD42F19BC227E1D247712F"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1" r:link="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9585325" y="1465122800"/>
-          <a:ext cx="15240000" cy="19050000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="ID_21E8FD03EA264997B0EE374C5ACB0FEF"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3" r:link="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9585325" y="1471041000"/>
-          <a:ext cx="15240000" cy="19050000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="ID_D08ABD960F664D71BFB066EA2296395A"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4" r:link="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10074910" y="1502410000"/>
-          <a:ext cx="15240000" cy="19050000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-</etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
